--- a/ig/DM-SIDOBA/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -762,13 +762,13 @@
     <t>157</t>
   </si>
   <si>
-    <t>Urgences polyvalentes</t>
+    <t>Urgences polyvalentes hospitalières</t>
   </si>
   <si>
     <t>158</t>
   </si>
   <si>
-    <t>Urgences psychiatriques</t>
+    <t>Urgences psychiatriques hospitalières</t>
   </si>
   <si>
     <t>159</t>
@@ -972,7 +972,7 @@
     <t>201</t>
   </si>
   <si>
-    <t>Pédicure-Podologie</t>
+    <t>Pédicurie-Podologie (bilan diagnostic et mise en œuvre des activités thérapeutiques si nécessaire)</t>
   </si>
   <si>
     <t>202</t>
@@ -1254,7 +1254,7 @@
     <t>249</t>
   </si>
   <si>
-    <t>Urgences pédiatriques</t>
+    <t>Urgences pédiatriques hospitalières</t>
   </si>
   <si>
     <t>250</t>
